--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-practitionerrole.xlsx
@@ -867,7 +867,7 @@
     <t>ユーザーに提示された理由は、なぜ時間が利用できないのかを説明しています / Reason presented to the user explaining why time not available</t>
   </si>
   <si>
-    <t>この時間が利用できない理由をユーザに提示することができる。</t>
+    <t>この時間が利用できない理由をユーザーに提示することができる。</t>
   </si>
   <si>
     <t>PractitionerRole.notAvailable.during</t>
